--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="146">
   <si>
     <t>怪物ID</t>
   </si>
@@ -49,6 +49,9 @@
     <t>攻击模式</t>
   </si>
   <si>
+    <t>怪物类型</t>
+  </si>
+  <si>
     <t>仇恨模式</t>
   </si>
   <si>
@@ -118,6 +121,9 @@
     <t>Melee | Ranged</t>
   </si>
   <si>
+    <t>1=普通(Normal) / 2=精英(Elite) / 3=BOSS(Boss)；缺列或空→1；非法→加载失败；异于 PushMapSpawnConfig.IsBoss；本批不驱动技能</t>
+  </si>
+  <si>
     <t>ActiveChase|PassiveChase|StationaryActive|StationaryPassive；空→ActiveChase</t>
   </si>
   <si>
@@ -187,6 +193,9 @@
     <t>AttackMode</t>
   </si>
   <si>
+    <t>MonsterType</t>
+  </si>
+  <si>
     <t>AggroMode</t>
   </si>
   <si>
@@ -458,6 +467,9 @@
   </si>
   <si>
     <t>骷髅猛士</t>
+  </si>
+  <si>
+    <t>Monster_12</t>
   </si>
 </sst>
 </file>
@@ -470,10 +482,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -932,154 +951,155 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1426,15 +1446,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.725" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1504,895 +1524,1008 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V2" t="s">
+        <v>45</v>
+      </c>
+      <c r="W2" t="s">
+        <v>46</v>
+      </c>
+      <c r="X2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:24">
+      <c r="A3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="A4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>0.15</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0.5</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>25</v>
       </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" t="s">
-        <v>37</v>
-      </c>
-      <c r="P2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>39</v>
-      </c>
-      <c r="R2" t="s">
-        <v>40</v>
-      </c>
-      <c r="S2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V2" t="s">
-        <v>44</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
+      <c r="N4" t="s">
+        <v>78</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>8</v>
+      </c>
+      <c r="R4" t="s">
+        <v>79</v>
+      </c>
+      <c r="S4" t="s">
+        <v>80</v>
+      </c>
+      <c r="T4" t="s">
+        <v>81</v>
+      </c>
+      <c r="U4" t="s">
+        <v>82</v>
+      </c>
+      <c r="V4" t="s">
+        <v>82</v>
+      </c>
+      <c r="X4" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:23">
-      <c r="A3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="1" t="s">
+    <row r="5" spans="1:24">
+      <c r="A5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>0.15</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>0.5</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>55</v>
+      </c>
+      <c r="N5" t="s">
+        <v>78</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>88</v>
+      </c>
+      <c r="R5" t="s">
+        <v>89</v>
+      </c>
+      <c r="S5" t="s">
+        <v>80</v>
+      </c>
+      <c r="T5" t="s">
+        <v>82</v>
+      </c>
+      <c r="U5" t="s">
+        <v>90</v>
+      </c>
+      <c r="V5" t="s">
+        <v>91</v>
+      </c>
+      <c r="X5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>0.15</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>0.5</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>85</v>
+      </c>
+      <c r="N6" t="s">
+        <v>78</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>96</v>
+      </c>
+      <c r="R6" t="s">
+        <v>97</v>
+      </c>
+      <c r="S6" t="s">
+        <v>80</v>
+      </c>
+      <c r="T6" t="s">
+        <v>98</v>
+      </c>
+      <c r="U6" t="s">
+        <v>82</v>
+      </c>
+      <c r="V6" t="s">
+        <v>82</v>
+      </c>
+      <c r="X6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
+      <c r="A7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>0.15</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>0.5</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>115</v>
+      </c>
+      <c r="N7" t="s">
+        <v>78</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>102</v>
+      </c>
+      <c r="R7" t="s">
+        <v>103</v>
+      </c>
+      <c r="S7" t="s">
+        <v>80</v>
+      </c>
+      <c r="T7" t="s">
+        <v>104</v>
+      </c>
+      <c r="U7" t="s">
+        <v>82</v>
+      </c>
+      <c r="V7" t="s">
+        <v>82</v>
+      </c>
+      <c r="X7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="A8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>0.15</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>0.5</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>145</v>
+      </c>
+      <c r="N8" t="s">
+        <v>78</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>108</v>
+      </c>
+      <c r="R8" t="s">
+        <v>109</v>
+      </c>
+      <c r="S8" t="s">
+        <v>80</v>
+      </c>
+      <c r="T8" t="s">
+        <v>82</v>
+      </c>
+      <c r="U8" t="s">
+        <v>102</v>
+      </c>
+      <c r="V8" t="s">
+        <v>91</v>
+      </c>
+      <c r="X8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>0.15</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>0.5</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>175</v>
+      </c>
+      <c r="N9" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>113</v>
+      </c>
+      <c r="R9" t="s">
+        <v>114</v>
+      </c>
+      <c r="S9" t="s">
+        <v>80</v>
+      </c>
+      <c r="T9" t="s">
+        <v>115</v>
+      </c>
+      <c r="U9" t="s">
+        <v>82</v>
+      </c>
+      <c r="V9" t="s">
+        <v>82</v>
+      </c>
+      <c r="X9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>0.15</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>0.5</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>205</v>
+      </c>
+      <c r="N10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>119</v>
+      </c>
+      <c r="R10" t="s">
+        <v>120</v>
+      </c>
+      <c r="S10" t="s">
+        <v>80</v>
+      </c>
+      <c r="T10" t="s">
+        <v>121</v>
+      </c>
+      <c r="U10" t="s">
+        <v>82</v>
+      </c>
+      <c r="V10" t="s">
+        <v>82</v>
+      </c>
+      <c r="X10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+      <c r="I11">
+        <v>0.15</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>0.5</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>235</v>
+      </c>
+      <c r="N11" t="s">
+        <v>78</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>125</v>
+      </c>
+      <c r="R11" t="s">
+        <v>126</v>
+      </c>
+      <c r="S11" t="s">
+        <v>80</v>
+      </c>
+      <c r="T11" t="s">
+        <v>82</v>
+      </c>
+      <c r="U11" t="s">
+        <v>127</v>
+      </c>
+      <c r="V11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>0.15</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>0.5</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>265</v>
+      </c>
+      <c r="N12" t="s">
+        <v>78</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>131</v>
+      </c>
+      <c r="R12" t="s">
+        <v>132</v>
+      </c>
+      <c r="S12" t="s">
+        <v>80</v>
+      </c>
+      <c r="T12" t="s">
+        <v>133</v>
+      </c>
+      <c r="U12" t="s">
+        <v>82</v>
+      </c>
+      <c r="V12" t="s">
+        <v>82</v>
+      </c>
+      <c r="X12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="A13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+      <c r="I13">
+        <v>0.15</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>0.5</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>295</v>
+      </c>
+      <c r="N13" t="s">
+        <v>78</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>137</v>
+      </c>
+      <c r="R13" t="s">
+        <v>138</v>
+      </c>
+      <c r="S13" t="s">
+        <v>139</v>
+      </c>
+      <c r="T13" t="s">
+        <v>140</v>
+      </c>
+      <c r="U13" t="s">
+        <v>82</v>
+      </c>
+      <c r="V13" t="s">
+        <v>82</v>
+      </c>
+      <c r="X13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
+      <c r="A14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14">
+        <v>10</v>
+      </c>
+      <c r="I14">
+        <v>0.3</v>
+      </c>
+      <c r="J14">
+        <v>1.1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>10000</v>
+      </c>
+      <c r="N14">
+        <v>0.3</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1500</v>
+      </c>
+      <c r="R14" t="s">
+        <v>138</v>
+      </c>
+      <c r="S14">
+        <v>0.35</v>
+      </c>
+      <c r="T14">
+        <v>1.25</v>
+      </c>
+      <c r="U14" t="s">
+        <v>82</v>
+      </c>
+      <c r="V14" t="s">
+        <v>82</v>
+      </c>
+      <c r="X14" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
+      <c r="A15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15">
+        <v>4</v>
+      </c>
+      <c r="I15">
+        <v>0.3</v>
+      </c>
+      <c r="J15">
+        <v>1.1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>3000</v>
+      </c>
+      <c r="N15">
+        <v>0.3</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
         <v>50</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K3" t="s">
-        <v>56</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N3" t="s">
-        <v>59</v>
-      </c>
-      <c r="O3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23">
-      <c r="A4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-      <c r="H4">
-        <v>0.15</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>0.5</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>25</v>
-      </c>
-      <c r="M4" t="s">
-        <v>75</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>8</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>76</v>
-      </c>
-      <c r="R4" t="s">
-        <v>77</v>
-      </c>
-      <c r="S4" t="s">
-        <v>78</v>
-      </c>
-      <c r="T4" t="s">
-        <v>79</v>
-      </c>
-      <c r="U4" t="s">
-        <v>79</v>
-      </c>
-      <c r="W4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23">
-      <c r="A5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="R15" t="s">
+        <v>138</v>
+      </c>
+      <c r="S15">
+        <v>0.35</v>
+      </c>
+      <c r="T15">
+        <v>1.25</v>
+      </c>
+      <c r="U15" t="s">
         <v>82</v>
       </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>0.15</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>0.5</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>55</v>
-      </c>
-      <c r="M5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>86</v>
-      </c>
-      <c r="R5" t="s">
-        <v>77</v>
-      </c>
-      <c r="S5" t="s">
-        <v>79</v>
-      </c>
-      <c r="T5" t="s">
-        <v>87</v>
-      </c>
-      <c r="U5" t="s">
-        <v>88</v>
-      </c>
-      <c r="W5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23">
-      <c r="A6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>0.15</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>0.5</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>85</v>
-      </c>
-      <c r="M6" t="s">
-        <v>75</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>94</v>
-      </c>
-      <c r="R6" t="s">
-        <v>77</v>
-      </c>
-      <c r="S6" t="s">
-        <v>95</v>
-      </c>
-      <c r="T6" t="s">
-        <v>79</v>
-      </c>
-      <c r="U6" t="s">
-        <v>79</v>
-      </c>
-      <c r="W6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
-      <c r="A7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>0.15</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>0.5</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>115</v>
-      </c>
-      <c r="M7" t="s">
-        <v>75</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>100</v>
-      </c>
-      <c r="R7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S7" t="s">
-        <v>101</v>
-      </c>
-      <c r="T7" t="s">
-        <v>79</v>
-      </c>
-      <c r="U7" t="s">
-        <v>79</v>
-      </c>
-      <c r="W7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23">
-      <c r="A8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>0.15</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>0.5</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>145</v>
-      </c>
-      <c r="M8" t="s">
-        <v>75</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>106</v>
-      </c>
-      <c r="R8" t="s">
-        <v>77</v>
-      </c>
-      <c r="S8" t="s">
-        <v>79</v>
-      </c>
-      <c r="T8" t="s">
-        <v>99</v>
-      </c>
-      <c r="U8" t="s">
-        <v>88</v>
-      </c>
-      <c r="W8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23">
-      <c r="A9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-      <c r="H9">
-        <v>0.15</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>0.5</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>175</v>
-      </c>
-      <c r="M9" t="s">
-        <v>75</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>111</v>
-      </c>
-      <c r="R9" t="s">
-        <v>77</v>
-      </c>
-      <c r="S9" t="s">
-        <v>112</v>
-      </c>
-      <c r="T9" t="s">
-        <v>79</v>
-      </c>
-      <c r="U9" t="s">
-        <v>79</v>
-      </c>
-      <c r="W9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23">
-      <c r="A10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-      <c r="H10">
-        <v>0.15</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>0.5</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>205</v>
-      </c>
-      <c r="M10" t="s">
-        <v>75</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-      <c r="P10" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>117</v>
-      </c>
-      <c r="R10" t="s">
-        <v>77</v>
-      </c>
-      <c r="S10" t="s">
-        <v>118</v>
-      </c>
-      <c r="T10" t="s">
-        <v>79</v>
-      </c>
-      <c r="U10" t="s">
-        <v>79</v>
-      </c>
-      <c r="W10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23">
-      <c r="A11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" t="s">
-        <v>74</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-      <c r="H11">
-        <v>0.15</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>0.5</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>235</v>
-      </c>
-      <c r="M11" t="s">
-        <v>75</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>123</v>
-      </c>
-      <c r="R11" t="s">
-        <v>77</v>
-      </c>
-      <c r="S11" t="s">
-        <v>79</v>
-      </c>
-      <c r="T11" t="s">
-        <v>124</v>
-      </c>
-      <c r="U11" t="s">
-        <v>88</v>
-      </c>
-      <c r="W11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23">
-      <c r="A12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-      <c r="H12">
-        <v>0.15</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <v>0.5</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>265</v>
-      </c>
-      <c r="M12" t="s">
-        <v>75</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>129</v>
-      </c>
-      <c r="R12" t="s">
-        <v>77</v>
-      </c>
-      <c r="S12" t="s">
-        <v>130</v>
-      </c>
-      <c r="T12" t="s">
-        <v>79</v>
-      </c>
-      <c r="U12" t="s">
-        <v>79</v>
-      </c>
-      <c r="W12" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23">
-      <c r="A13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>133</v>
-      </c>
-      <c r="D13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-      <c r="H13">
-        <v>0.15</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <v>0.5</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>295</v>
-      </c>
-      <c r="M13" t="s">
-        <v>75</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-      <c r="P13" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>135</v>
-      </c>
-      <c r="R13" t="s">
-        <v>136</v>
-      </c>
-      <c r="S13" t="s">
-        <v>137</v>
-      </c>
-      <c r="T13" t="s">
-        <v>79</v>
-      </c>
-      <c r="U13" t="s">
-        <v>79</v>
-      </c>
-      <c r="W13" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23">
-      <c r="A14" t="s">
-        <v>139</v>
-      </c>
-      <c r="B14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="V15" t="s">
+        <v>82</v>
+      </c>
+      <c r="X15" t="s">
         <v>141</v>
-      </c>
-      <c r="D14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14">
-        <v>10</v>
-      </c>
-      <c r="H14">
-        <v>0.3</v>
-      </c>
-      <c r="I14">
-        <v>1.5</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>10000</v>
-      </c>
-      <c r="M14">
-        <v>0.3</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14">
-        <v>1</v>
-      </c>
-      <c r="P14">
-        <v>1500</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>135</v>
-      </c>
-      <c r="R14">
-        <v>0.45</v>
-      </c>
-      <c r="S14">
-        <v>1.25</v>
-      </c>
-      <c r="T14" t="s">
-        <v>79</v>
-      </c>
-      <c r="U14" t="s">
-        <v>79</v>
-      </c>
-      <c r="W14" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="174">
   <si>
     <t>怪物ID</t>
   </si>
@@ -444,34 +444,22 @@
     <t>Monster_04</t>
   </si>
   <si>
-    <t>幽魂</t>
-  </si>
-  <si>
-    <t>115</t>
+    <t>Monster_05</t>
+  </si>
+  <si>
+    <t>石像鬼</t>
+  </si>
+  <si>
+    <t>PreferWarrior</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>14</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>0.36</t>
-  </si>
-  <si>
-    <t>Monster_05</t>
-  </si>
-  <si>
-    <t>石像鬼</t>
-  </si>
-  <si>
-    <t>PreferWarrior</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
-    <t>16</t>
   </si>
   <si>
     <t>Monster_06</t>
@@ -2131,10 +2119,10 @@
         <v>125</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>126</v>
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
       </c>
       <c r="D7" t="s">
         <v>90</v>
@@ -2148,8 +2136,8 @@
       <c r="G7" t="s">
         <v>93</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>94</v>
+      <c r="H7" s="2">
+        <v>10</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>95</v>
@@ -2164,7 +2152,7 @@
         <v>97</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>96</v>
@@ -2182,22 +2170,25 @@
         <v>92</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>102</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="W7" t="s">
         <v>97</v>
       </c>
       <c r="X7" t="s">
         <v>97</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>104</v>
       </c>
       <c r="Z7" t="s">
         <v>105</v>
@@ -2211,16 +2202,16 @@
     </row>
     <row r="8" spans="1:29">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s">
         <v>118</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E8" t="s">
         <v>111</v>
@@ -2247,7 +2238,7 @@
         <v>97</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>96</v>
@@ -2265,7 +2256,7 @@
         <v>92</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>92</v>
@@ -2277,7 +2268,7 @@
         <v>97</v>
       </c>
       <c r="W8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="X8" t="s">
         <v>116</v>
@@ -2294,13 +2285,13 @@
     </row>
     <row r="9" spans="1:29">
       <c r="A9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s">
         <v>118</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
@@ -2330,7 +2321,7 @@
         <v>97</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>96</v>
@@ -2348,16 +2339,16 @@
         <v>92</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>102</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="W9" t="s">
         <v>97</v>
@@ -2377,13 +2368,13 @@
     </row>
     <row r="10" spans="1:29">
       <c r="A10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s">
         <v>118</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s">
         <v>90</v>
@@ -2413,7 +2404,7 @@
         <v>97</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>96</v>
@@ -2431,16 +2422,16 @@
         <v>92</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>102</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="W10" t="s">
         <v>97</v>
@@ -2460,16 +2451,16 @@
     </row>
     <row r="11" spans="1:29">
       <c r="A11" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s">
         <v>118</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
         <v>111</v>
@@ -2496,7 +2487,7 @@
         <v>97</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>96</v>
@@ -2514,10 +2505,10 @@
         <v>92</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>102</v>
@@ -2526,7 +2517,7 @@
         <v>97</v>
       </c>
       <c r="W11" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="X11" t="s">
         <v>116</v>
@@ -2543,13 +2534,13 @@
     </row>
     <row r="12" spans="1:29">
       <c r="A12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s">
         <v>118</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s">
         <v>120</v>
@@ -2579,7 +2570,7 @@
         <v>97</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>96</v>
@@ -2597,16 +2588,16 @@
         <v>92</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="U12" s="2" t="s">
         <v>102</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="W12" t="s">
         <v>97</v>
@@ -2626,13 +2617,13 @@
     </row>
     <row r="13" spans="1:29">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s">
         <v>118</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
         <v>90</v>
@@ -2662,7 +2653,7 @@
         <v>97</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>96</v>
@@ -2680,16 +2671,16 @@
         <v>92</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="W13" t="s">
         <v>97</v>
@@ -2709,13 +2700,13 @@
     </row>
     <row r="14" spans="1:29">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C14" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D14" t="s">
         <v>90</v>
@@ -2730,13 +2721,13 @@
         <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>103</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>92</v>
@@ -2745,13 +2736,13 @@
         <v>97</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>103</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>96</v>
@@ -2763,16 +2754,16 @@
         <v>92</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="W14" t="s">
         <v>97</v>
@@ -2792,7 +2783,7 @@
     </row>
     <row r="15" spans="1:29">
       <c r="A15" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s">
         <v>109</v>
@@ -2819,7 +2810,7 @@
         <v>103</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>92</v>
@@ -2828,13 +2819,13 @@
         <v>97</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>103</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>96</v>
@@ -2846,16 +2837,16 @@
         <v>92</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="W15" t="s">
         <v>97</v>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="175">
   <si>
     <t>怪物ID</t>
   </si>
@@ -442,6 +442,9 @@
   </si>
   <si>
     <t>Monster_04</t>
+  </si>
+  <si>
+    <t>MSkill_SelfRevive_1;0</t>
   </si>
   <si>
     <t>Monster_05</t>
@@ -2188,7 +2191,7 @@
         <v>97</v>
       </c>
       <c r="Y7" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="Z7" t="s">
         <v>105</v>
@@ -2202,16 +2205,16 @@
     </row>
     <row r="8" spans="1:29">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s">
         <v>118</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E8" t="s">
         <v>111</v>
@@ -2238,7 +2241,7 @@
         <v>97</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>96</v>
@@ -2256,7 +2259,7 @@
         <v>92</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>92</v>
@@ -2268,7 +2271,7 @@
         <v>97</v>
       </c>
       <c r="W8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="X8" t="s">
         <v>116</v>
@@ -2285,13 +2288,13 @@
     </row>
     <row r="9" spans="1:29">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s">
         <v>118</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
@@ -2321,7 +2324,7 @@
         <v>97</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>96</v>
@@ -2339,16 +2342,16 @@
         <v>92</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>102</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="W9" t="s">
         <v>97</v>
@@ -2368,13 +2371,13 @@
     </row>
     <row r="10" spans="1:29">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s">
         <v>118</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s">
         <v>90</v>
@@ -2404,7 +2407,7 @@
         <v>97</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>96</v>
@@ -2422,16 +2425,16 @@
         <v>92</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>102</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="W10" t="s">
         <v>97</v>
@@ -2451,16 +2454,16 @@
     </row>
     <row r="11" spans="1:29">
       <c r="A11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s">
         <v>118</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E11" t="s">
         <v>111</v>
@@ -2487,7 +2490,7 @@
         <v>97</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>96</v>
@@ -2505,10 +2508,10 @@
         <v>92</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>102</v>
@@ -2517,7 +2520,7 @@
         <v>97</v>
       </c>
       <c r="W11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="X11" t="s">
         <v>116</v>
@@ -2534,13 +2537,13 @@
     </row>
     <row r="12" spans="1:29">
       <c r="A12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s">
         <v>118</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s">
         <v>120</v>
@@ -2570,7 +2573,7 @@
         <v>97</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>96</v>
@@ -2588,16 +2591,16 @@
         <v>92</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="U12" s="2" t="s">
         <v>102</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="W12" t="s">
         <v>97</v>
@@ -2617,13 +2620,13 @@
     </row>
     <row r="13" spans="1:29">
       <c r="A13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s">
         <v>118</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D13" t="s">
         <v>90</v>
@@ -2653,7 +2656,7 @@
         <v>97</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>96</v>
@@ -2671,16 +2674,16 @@
         <v>92</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="W13" t="s">
         <v>97</v>
@@ -2700,13 +2703,13 @@
     </row>
     <row r="14" spans="1:29">
       <c r="A14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D14" t="s">
         <v>90</v>
@@ -2721,13 +2724,13 @@
         <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>103</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>92</v>
@@ -2736,13 +2739,13 @@
         <v>97</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>103</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>96</v>
@@ -2754,16 +2757,16 @@
         <v>92</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="W14" t="s">
         <v>97</v>
@@ -2783,7 +2786,7 @@
     </row>
     <row r="15" spans="1:29">
       <c r="A15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s">
         <v>109</v>
@@ -2810,7 +2813,7 @@
         <v>103</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>92</v>
@@ -2819,13 +2822,13 @@
         <v>97</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>103</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>96</v>
@@ -2837,16 +2840,16 @@
         <v>92</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="W15" t="s">
         <v>97</v>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -41,20 +41,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>JM:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>JM:
 MonsterModel_05;70|MonsterModel_02;30</t>
         </r>
       </text>
@@ -64,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="182">
   <si>
     <t>怪物ID</t>
   </si>
@@ -153,6 +144,9 @@
     <t>怪物掉落</t>
   </si>
   <si>
+    <t>士兵简画图标</t>
+  </si>
+  <si>
     <t>主键；被 WaveSpawnConfig / PushMapSpawnConfig 引用</t>
   </si>
   <si>
@@ -240,6 +234,9 @@
     <t>击杀产出；编码 Id;Count|Id;Count|…</t>
   </si>
   <si>
+    <t>UI-033 战斗指示器简画；仅文件名；Resources/UI/Icons/{Id}；空=空框</t>
+  </si>
+  <si>
     <t>MonsterId</t>
   </si>
   <si>
@@ -327,6 +324,9 @@
     <t>LootDrop</t>
   </si>
   <si>
+    <t>SilhouetteIconAssetId</t>
+  </si>
+  <si>
     <t>Monster_01</t>
   </si>
   <si>
@@ -390,6 +390,9 @@
     <t>Run</t>
   </si>
   <si>
+    <t>HPPK_UI_Monster_01</t>
+  </si>
+  <si>
     <t>Monster_02</t>
   </si>
   <si>
@@ -417,6 +420,9 @@
     <t>2.5</t>
   </si>
   <si>
+    <t>HPPK_UI_Monster_02</t>
+  </si>
+  <si>
     <t>Monster_03</t>
   </si>
   <si>
@@ -441,10 +447,16 @@
     <t>0.34</t>
   </si>
   <si>
+    <t>HPPK_UI_Monster_03</t>
+  </si>
+  <si>
     <t>Monster_04</t>
   </si>
   <si>
     <t>MSkill_SelfRevive_1;0</t>
+  </si>
+  <si>
+    <t>HPPK_UI_Monster_04</t>
   </si>
   <si>
     <t>Monster_05</t>
@@ -601,7 +613,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -767,13 +779,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1586,7 +1592,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AD15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.725" customWidth="1"/>
@@ -1598,7 +1604,7 @@
     <col min="26" max="26" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:30">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1686,1185 +1692,1230 @@
       <c r="AC1" t="s">
         <v>28</v>
       </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="X2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AB2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AC2" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:29">
+    <row r="3" s="1" customFormat="1" spans="1:30">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:29">
+    <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="W4" t="s">
+        <v>100</v>
+      </c>
+      <c r="X4" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30">
+      <c r="A5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="W5" t="s">
+        <v>119</v>
+      </c>
+      <c r="X5" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
+      <c r="A6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="W6" t="s">
+        <v>100</v>
+      </c>
+      <c r="X6" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="C7" t="s">
         <v>92</v>
       </c>
-      <c r="G4" t="s">
+      <c r="D7" t="s">
         <v>93</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="E7" t="s">
         <v>94</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K4" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" t="s">
         <v>96</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="W4" t="s">
-        <v>97</v>
-      </c>
-      <c r="X4" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29">
-      <c r="A5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" t="s">
-        <v>93</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="W5" t="s">
-        <v>115</v>
-      </c>
-      <c r="X5" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29">
-      <c r="A6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G6" t="s">
-        <v>93</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="W6" t="s">
-        <v>97</v>
-      </c>
-      <c r="X6" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29">
-      <c r="A7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G7" t="s">
-        <v>93</v>
       </c>
       <c r="H7" s="2">
         <v>10</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="W7" t="s">
+        <v>100</v>
+      </c>
+      <c r="X7" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30">
+      <c r="A8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" t="s">
         <v>96</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="J8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="W8" t="s">
+        <v>139</v>
+      </c>
+      <c r="X8" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30">
+      <c r="A9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" t="s">
         <v>96</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P7" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="W9" t="s">
+        <v>100</v>
+      </c>
+      <c r="X9" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30">
+      <c r="A10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10" t="s">
         <v>96</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="U7" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="W7" t="s">
+      <c r="P10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="W10" t="s">
+        <v>100</v>
+      </c>
+      <c r="X10" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30">
+      <c r="A11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="X7" t="s">
+      <c r="I11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="W11" t="s">
+        <v>157</v>
+      </c>
+      <c r="X11" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30">
+      <c r="A12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" t="s">
+        <v>96</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="Y7" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z7" t="s">
+      <c r="I12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="U12" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="V12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="W12" t="s">
+        <v>100</v>
+      </c>
+      <c r="X12" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30">
+      <c r="A13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="W13" t="s">
+        <v>100</v>
+      </c>
+      <c r="X13" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30">
+      <c r="A14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" t="s">
+        <v>96</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AB7" t="s">
-        <v>107</v>
+      <c r="J14" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="W14" t="s">
+        <v>100</v>
+      </c>
+      <c r="X14" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>130</v>
       </c>
     </row>
-    <row r="8" spans="1:29">
-      <c r="A8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8" t="s">
-        <v>111</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G8" t="s">
+    <row r="15" spans="1:30">
+      <c r="A15" t="s">
+        <v>179</v>
+      </c>
+      <c r="B15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" t="s">
         <v>93</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="E15" t="s">
         <v>94</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K8" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" t="s">
         <v>96</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="W8" t="s">
-        <v>132</v>
-      </c>
-      <c r="X8" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA8" t="s">
+      <c r="I15" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AB8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29">
-      <c r="A9" t="s">
+      <c r="J15" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="W15" t="s">
+        <v>100</v>
+      </c>
+      <c r="X15" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD15" t="s">
         <v>133</v>
-      </c>
-      <c r="B9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="W9" t="s">
-        <v>97</v>
-      </c>
-      <c r="X9" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29">
-      <c r="A10" t="s">
-        <v>139</v>
-      </c>
-      <c r="B10" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" t="s">
-        <v>93</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="W10" t="s">
-        <v>97</v>
-      </c>
-      <c r="X10" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29">
-      <c r="A11" t="s">
-        <v>145</v>
-      </c>
-      <c r="B11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E11" t="s">
-        <v>111</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G11" t="s">
-        <v>93</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="W11" t="s">
-        <v>150</v>
-      </c>
-      <c r="X11" t="s">
-        <v>116</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29">
-      <c r="A12" t="s">
-        <v>151</v>
-      </c>
-      <c r="B12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" t="s">
-        <v>91</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="W12" t="s">
-        <v>97</v>
-      </c>
-      <c r="X12" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29">
-      <c r="A13" t="s">
-        <v>157</v>
-      </c>
-      <c r="B13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G13" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="W13" t="s">
-        <v>97</v>
-      </c>
-      <c r="X13" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29">
-      <c r="A14" t="s">
-        <v>164</v>
-      </c>
-      <c r="B14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C14" t="s">
-        <v>166</v>
-      </c>
-      <c r="D14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" t="s">
-        <v>91</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G14" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="W14" t="s">
-        <v>97</v>
-      </c>
-      <c r="X14" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29">
-      <c r="A15" t="s">
-        <v>172</v>
-      </c>
-      <c r="B15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" t="s">
-        <v>91</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G15" t="s">
-        <v>93</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="U15" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="W15" t="s">
-        <v>97</v>
-      </c>
-      <c r="X15" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="181">
   <si>
     <t>怪物ID</t>
   </si>
@@ -378,7 +378,7 @@
     <t>0.3</t>
   </si>
   <si>
-    <t>MSkill_SelfRevive_99;0</t>
+    <t>MSkill_SelfRevive_1;0</t>
   </si>
   <si>
     <t>Attack1|Attack2|Attack3|Attack4</t>
@@ -451,9 +451,6 @@
   </si>
   <si>
     <t>Monster_04</t>
-  </si>
-  <si>
-    <t>MSkill_SelfRevive_1;0</t>
   </si>
   <si>
     <t>HPPK_UI_Monster_04</t>
@@ -2215,7 +2212,7 @@
         <v>100</v>
       </c>
       <c r="Y7" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="Z7" t="s">
         <v>108</v>
@@ -2227,21 +2224,21 @@
         <v>110</v>
       </c>
       <c r="AD7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B8" t="s">
         <v>123</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" t="s">
         <v>135</v>
-      </c>
-      <c r="D8" t="s">
-        <v>136</v>
       </c>
       <c r="E8" t="s">
         <v>115</v>
@@ -2268,7 +2265,7 @@
         <v>100</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>99</v>
@@ -2286,7 +2283,7 @@
         <v>95</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>95</v>
@@ -2298,7 +2295,7 @@
         <v>100</v>
       </c>
       <c r="W8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X8" t="s">
         <v>120</v>
@@ -2318,13 +2315,13 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s">
         <v>123</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D9" t="s">
         <v>125</v>
@@ -2354,7 +2351,7 @@
         <v>100</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>99</v>
@@ -2372,16 +2369,16 @@
         <v>95</v>
       </c>
       <c r="S9" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>105</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="W9" t="s">
         <v>100</v>
@@ -2404,13 +2401,13 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s">
         <v>123</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s">
         <v>93</v>
@@ -2440,7 +2437,7 @@
         <v>100</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>99</v>
@@ -2458,16 +2455,16 @@
         <v>95</v>
       </c>
       <c r="S10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="T10" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>105</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="W10" t="s">
         <v>100</v>
@@ -2490,16 +2487,16 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s">
         <v>123</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E11" t="s">
         <v>115</v>
@@ -2526,7 +2523,7 @@
         <v>100</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>99</v>
@@ -2544,10 +2541,10 @@
         <v>95</v>
       </c>
       <c r="S11" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="T11" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>105</v>
@@ -2556,7 +2553,7 @@
         <v>100</v>
       </c>
       <c r="W11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X11" t="s">
         <v>120</v>
@@ -2571,18 +2568,18 @@
         <v>110</v>
       </c>
       <c r="AD11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s">
         <v>123</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="s">
         <v>125</v>
@@ -2612,7 +2609,7 @@
         <v>100</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>99</v>
@@ -2630,16 +2627,16 @@
         <v>95</v>
       </c>
       <c r="S12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="T12" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="U12" s="2" t="s">
         <v>105</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="W12" t="s">
         <v>100</v>
@@ -2662,13 +2659,13 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s">
         <v>123</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D13" t="s">
         <v>93</v>
@@ -2698,7 +2695,7 @@
         <v>100</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>99</v>
@@ -2716,16 +2713,16 @@
         <v>95</v>
       </c>
       <c r="S13" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="T13" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="T13" s="2" t="s">
+      <c r="U13" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="U13" s="2" t="s">
+      <c r="V13" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="W13" t="s">
         <v>100</v>
@@ -2748,13 +2745,13 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
+        <v>170</v>
+      </c>
+      <c r="B14" t="s">
         <v>171</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>172</v>
-      </c>
-      <c r="C14" t="s">
-        <v>173</v>
       </c>
       <c r="D14" t="s">
         <v>93</v>
@@ -2769,13 +2766,13 @@
         <v>96</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>106</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>95</v>
@@ -2784,34 +2781,34 @@
         <v>100</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>106</v>
       </c>
       <c r="O14" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="S14" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="S14" s="2" t="s">
+      <c r="T14" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="U14" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="T14" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="V14" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W14" t="s">
         <v>100</v>
@@ -2834,7 +2831,7 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s">
         <v>113</v>
@@ -2861,7 +2858,7 @@
         <v>106</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>95</v>
@@ -2870,13 +2867,13 @@
         <v>100</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>106</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>99</v>
@@ -2888,16 +2885,16 @@
         <v>95</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W15" t="s">
         <v>100</v>
@@ -2915,7 +2912,7 @@
         <v>110</v>
       </c>
       <c r="AD15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
